--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>129688642</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129688640</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129688221</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129688641</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129688217</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129688214</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>129688644</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>129688215</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129688216</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>129688642</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129688640</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129688221</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129688641</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129688217</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129688214</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>129688644</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>129688215</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129688216</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129688642</v>
+        <v>129688640</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>792497</v>
+        <v>792576</v>
       </c>
       <c r="R8" t="n">
-        <v>7304536</v>
+        <v>7304584</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129688640</v>
+        <v>129688642</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>792576</v>
+        <v>792497</v>
       </c>
       <c r="R9" t="n">
-        <v>7304584</v>
+        <v>7304536</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1532,7 @@
         <v>129688221</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129688641</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129688217</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129688214</v>
       </c>
       <c r="B13" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>129688644</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>129688215</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129688216</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129688640</v>
+        <v>129688642</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>792576</v>
+        <v>792497</v>
       </c>
       <c r="R8" t="n">
-        <v>7304584</v>
+        <v>7304536</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129688642</v>
+        <v>129688640</v>
       </c>
       <c r="B9" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>792497</v>
+        <v>792576</v>
       </c>
       <c r="R9" t="n">
-        <v>7304536</v>
+        <v>7304584</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,7 +1532,7 @@
         <v>129688221</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129688641</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129688217</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129688214</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>129688644</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>129688215</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129688216</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>129688642</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129688640</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129688221</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129688641</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129688217</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129688214</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>129688644</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>129688215</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129688216</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>129688642</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129688640</v>
       </c>
       <c r="B9" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129688221</v>
       </c>
       <c r="B10" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129688641</v>
       </c>
       <c r="B11" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129688217</v>
       </c>
       <c r="B12" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129688214</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>129688644</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>129688215</v>
       </c>
       <c r="B15" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129688216</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>129688642</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129688640</v>
       </c>
       <c r="B9" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129688221</v>
       </c>
       <c r="B10" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129688641</v>
       </c>
       <c r="B11" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129688217</v>
       </c>
       <c r="B12" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129688214</v>
       </c>
       <c r="B13" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>129688644</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>129688215</v>
       </c>
       <c r="B15" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129688216</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -1320,7 +1320,7 @@
         <v>129688642</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>129688640</v>
       </c>
       <c r="B9" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129688221</v>
       </c>
       <c r="B10" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129688641</v>
       </c>
       <c r="B11" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>129688217</v>
       </c>
       <c r="B12" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129688214</v>
       </c>
       <c r="B13" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>129688644</v>
       </c>
       <c r="B14" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>129688215</v>
       </c>
       <c r="B15" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>129688216</v>
       </c>
       <c r="B16" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110045958</v>
+        <v>110045970</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>792529.3871260042</v>
+        <v>792402</v>
       </c>
       <c r="R2" t="n">
-        <v>7304585.014602653</v>
+        <v>7304516</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-06-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129001207</v>
+        <v>129688689</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -826,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>792511</v>
+        <v>792377</v>
       </c>
       <c r="R3" t="n">
-        <v>7304571</v>
+        <v>7304491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -893,32 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129001214</v>
+        <v>86421697</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -932,13 +917,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>792469</v>
+        <v>792398</v>
       </c>
       <c r="R4" t="n">
-        <v>7304522</v>
+        <v>7304508</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,17 +947,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2019-11-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2019-11-07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>Påträffad under Sveaskogs inventering.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,49 +984,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129001209</v>
+        <v>110045957</v>
       </c>
       <c r="B5" t="n">
-        <v>98727</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Alträsk, Nb</t>
+          <t>Stor-Alberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>792564</v>
+        <v>792471</v>
       </c>
       <c r="R5" t="n">
-        <v>7304575</v>
+        <v>7304625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,17 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,61 +1069,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129001208</v>
+        <v>110045967</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Alträsk, Nb</t>
+          <t>Stor-Alberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>792573</v>
+        <v>792404</v>
       </c>
       <c r="R6" t="n">
-        <v>7304602</v>
+        <v>7304506</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,17 +1146,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,44 +1166,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129001210</v>
+        <v>129224228</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1250,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>792574</v>
+        <v>792458</v>
       </c>
       <c r="R7" t="n">
-        <v>7304514</v>
+        <v>7304627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,12 +1247,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1317,37 +1284,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129688642</v>
+        <v>129224229</v>
       </c>
       <c r="B8" t="n">
-        <v>98815</v>
+        <v>80461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1356,10 +1323,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>792497</v>
+        <v>792452</v>
       </c>
       <c r="R8" t="n">
-        <v>7304536</v>
+        <v>7304625</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,12 +1353,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1423,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129688640</v>
+        <v>110045958</v>
       </c>
       <c r="B9" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,21 +1418,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Alträsk, Nb</t>
+          <t>Stor-Alberget, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>792576</v>
+        <v>792529</v>
       </c>
       <c r="R9" t="n">
-        <v>7304584</v>
+        <v>7304585</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,17 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1517,22 +1475,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129688221</v>
+        <v>110045969</v>
       </c>
       <c r="B10" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,21 +1515,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Alträsk, Nb</t>
+          <t>Stor-Alberget, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>792463</v>
+        <v>792409</v>
       </c>
       <c r="R10" t="n">
-        <v>7304520</v>
+        <v>7304507</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,17 +1552,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2022-06-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,22 +1572,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Robert Sandberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129688641</v>
+        <v>129001207</v>
       </c>
       <c r="B11" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,7 +1614,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1674,10 +1623,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>792566</v>
+        <v>792511</v>
       </c>
       <c r="R11" t="n">
-        <v>7304547</v>
+        <v>7304571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1704,12 +1653,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1741,10 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129688217</v>
+        <v>129001208</v>
       </c>
       <c r="B12" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,10 +1729,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>792585</v>
+        <v>792573</v>
       </c>
       <c r="R12" t="n">
-        <v>7304512</v>
+        <v>7304602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1847,10 +1796,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129688214</v>
+        <v>129001209</v>
       </c>
       <c r="B13" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>792525</v>
+        <v>792564</v>
       </c>
       <c r="R13" t="n">
-        <v>7304574</v>
+        <v>7304575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,10 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129688644</v>
+        <v>129001210</v>
       </c>
       <c r="B14" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1983,7 +1932,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1992,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>792491</v>
+        <v>792574</v>
       </c>
       <c r="R14" t="n">
-        <v>7304488</v>
+        <v>7304514</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2022,12 +1971,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2059,10 +2008,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129688215</v>
+        <v>129001214</v>
       </c>
       <c r="B15" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2098,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>792579</v>
+        <v>792469</v>
       </c>
       <c r="R15" t="n">
-        <v>7304605</v>
+        <v>7304522</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2165,10 +2114,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129688216</v>
+        <v>129688214</v>
       </c>
       <c r="B16" t="n">
-        <v>98815</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2204,10 +2153,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>792563</v>
+        <v>792525</v>
       </c>
       <c r="R16" t="n">
-        <v>7304563</v>
+        <v>7304574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,6 +2217,1269 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129688215</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>792579</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7304605</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129688216</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>792563</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7304563</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129688217</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>792585</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7304512</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129688221</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>792463</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7304520</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129688640</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>792576</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7304584</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129688641</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>792566</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7304547</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129688642</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>792497</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7304536</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129688644</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>792491</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7304488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129688651</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>792391</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7304511</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129688652</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>792410</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7304549</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129688653</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>792437</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7304580</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>110045960</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stor-Alberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>792604</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7304615</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-06-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-06-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57526-2025 artfynd.xlsx
+++ b/artfynd/A 57526-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045970</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688689</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86421697</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,6 +1098,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045957</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045967</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224228</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129224229</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045958</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045960</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110045969</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001207</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1890,6 +1950,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001208</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1996,6 +2061,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001209</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001210</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2208,6 +2283,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001214</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2314,6 +2394,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688214</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2420,6 +2505,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688215</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2526,6 +2616,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688216</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2632,6 +2727,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688217</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2738,6 +2838,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688221</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2844,6 +2949,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688640</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2950,6 +3060,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688641</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3056,6 +3171,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688642</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3162,6 +3282,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688644</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3268,6 +3393,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688651</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3374,6 +3504,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688652</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3480,8 +3615,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688653</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>